--- a/artfynd/A 56054-2025 artfynd.xlsx
+++ b/artfynd/A 56054-2025 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>129173083</v>
       </c>
       <c r="B6" t="n">
-        <v>80048</v>
+        <v>80053</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 56054-2025 artfynd.xlsx
+++ b/artfynd/A 56054-2025 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>129173083</v>
       </c>
       <c r="B6" t="n">
-        <v>80053</v>
+        <v>80054</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 56054-2025 artfynd.xlsx
+++ b/artfynd/A 56054-2025 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>129173083</v>
       </c>
       <c r="B6" t="n">
-        <v>80054</v>
+        <v>80059</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 56054-2025 artfynd.xlsx
+++ b/artfynd/A 56054-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1162,6 +1162,103 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130024669</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98797</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tollsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>428417</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6683880</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56054-2025 artfynd.xlsx
+++ b/artfynd/A 56054-2025 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>130024669</v>
       </c>
       <c r="B7" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56054-2025 artfynd.xlsx
+++ b/artfynd/A 56054-2025 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>130024669</v>
       </c>
       <c r="B7" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56054-2025 artfynd.xlsx
+++ b/artfynd/A 56054-2025 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>130024669</v>
       </c>
       <c r="B7" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56054-2025 artfynd.xlsx
+++ b/artfynd/A 56054-2025 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>130024669</v>
       </c>
       <c r="B7" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56054-2025 artfynd.xlsx
+++ b/artfynd/A 56054-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129173075</v>
+        <v>129173080</v>
       </c>
       <c r="B2" t="n">
-        <v>80135</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229497</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428373</v>
+        <v>428426</v>
       </c>
       <c r="R2" t="n">
-        <v>6684145</v>
+        <v>6683938</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129173074</v>
+        <v>129173082</v>
       </c>
       <c r="B3" t="n">
-        <v>80135</v>
+        <v>80305</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>392</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428358</v>
+        <v>428401</v>
       </c>
       <c r="R3" t="n">
-        <v>6683854</v>
+        <v>6683870</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,45 +869,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129173076</v>
+        <v>129173083</v>
       </c>
       <c r="B4" t="n">
-        <v>80110</v>
+        <v>80305</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6457</v>
+        <v>392</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tollsjöberget, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428374</v>
+        <v>428403</v>
       </c>
       <c r="R4" t="n">
-        <v>6684146</v>
+        <v>6683832</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,6 +951,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -966,32 +970,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129173082</v>
+        <v>129173076</v>
       </c>
       <c r="B5" t="n">
-        <v>80048</v>
+        <v>80367</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>392</v>
+        <v>6457</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428401</v>
+        <v>428374</v>
       </c>
       <c r="R5" t="n">
-        <v>6683870</v>
+        <v>6684146</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,48 +1067,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129173083</v>
+        <v>129173077</v>
       </c>
       <c r="B6" t="n">
-        <v>80059</v>
+        <v>80461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>392</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tollsjöberget, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428403</v>
+        <v>428385</v>
       </c>
       <c r="R6" t="n">
-        <v>6683832</v>
+        <v>6684147</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1145,7 +1146,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1167,7 +1167,7 @@
         <v>130024669</v>
       </c>
       <c r="B7" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,6 +1258,200 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129173074</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tollsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>428358</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6683854</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129173075</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tollsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>428373</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6684145</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56054-2025 artfynd.xlsx
+++ b/artfynd/A 56054-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173080</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173082</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173083</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173076</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173077</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130024669</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173074</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,8 +1492,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173075</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>